--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487754_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487754_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4976</v>
+        <v>5.7517</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8117</v>
+        <v>4.7932</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.9585</v>
       </c>
       <c r="G2" t="n">
         <v>3.4029</v>
@@ -610,13 +610,13 @@
         <v>2.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5933</v>
+        <v>-0.3393</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.544</v>
+        <v>-0.5625</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0493</v>
+        <v>0.2232</v>
       </c>
       <c r="V2" t="n">
         <v>0.9418</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5575</v>
+        <v>2.5848</v>
       </c>
       <c r="E3" t="n">
         <v>1.4477</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1099</v>
+        <v>1.1371</v>
       </c>
       <c r="G3" t="n">
         <v>2.3577</v>
@@ -688,13 +688,13 @@
         <v>0.194</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0058</v>
+        <v>0.0331</v>
       </c>
       <c r="T3" t="n">
         <v>-0.1817</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1875</v>
+        <v>0.2148</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3899</v>
+        <v>2.3897</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6826</v>
+        <v>0.7642</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7073</v>
+        <v>1.6255</v>
       </c>
       <c r="G4" t="n">
         <v>1.9157</v>
@@ -766,13 +766,13 @@
         <v>2.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1519</v>
+        <v>0.1517</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4711</v>
+        <v>-0.3895</v>
       </c>
       <c r="U4" t="n">
-        <v>0.623</v>
+        <v>0.5412</v>
       </c>
       <c r="V4" t="n">
         <v>0.5164</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9059</v>
+        <v>1.8423</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2396</v>
+        <v>0.4213</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6663</v>
+        <v>1.421</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3545</v>
@@ -844,13 +844,13 @@
         <v>1.7463</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2604</v>
+        <v>0.1968</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.35</v>
+        <v>-0.1683</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.3651</v>
       </c>
       <c r="V5" t="n">
         <v>1.2239</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.763</v>
+        <v>1.7173</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4705</v>
+        <v>-0.489</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2335</v>
+        <v>2.2063</v>
       </c>
       <c r="G6" t="n">
         <v>1.3249</v>
@@ -922,13 +922,13 @@
         <v>2.1344</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1276</v>
+        <v>0.0819</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3623</v>
+        <v>-0.3808</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4899</v>
+        <v>0.4627</v>
       </c>
       <c r="V6" t="n">
         <v>-0.6597</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7513</v>
+        <v>1.7082</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6333</v>
+        <v>1.5358</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1179</v>
+        <v>0.1724</v>
       </c>
       <c r="G7" t="n">
         <v>0.6079</v>
@@ -1000,13 +1000,13 @@
         <v>2.1344</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.5765</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0145</v>
+        <v>-0.083</v>
       </c>
       <c r="U7" t="n">
-        <v>0.605</v>
+        <v>0.6595</v>
       </c>
       <c r="V7" t="n">
         <v>0.3299</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5763</v>
+        <v>-0.4884</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7279</v>
+        <v>-0.6673</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1516</v>
+        <v>0.1789</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5339</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0424</v>
+        <v>0.0454</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0606</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. LARDIES GUILLEN</t>
+          <t>J. DE DOMINGO GARAY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3437</v>
+        <v>-0.8796</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1202</v>
+        <v>-0.0901</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2235</v>
+        <v>-0.7895</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8696</v>
+        <v>-1.324</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.4286</v>
+        <v>-0.1467</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.441</v>
+        <v>-1.1773</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0418</v>
+        <v>-0.1324</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3872</v>
+        <v>0.4943</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6546</v>
+        <v>-0.6267</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.9114</v>
+        <v>-1.1916</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.8158</v>
+        <v>-0.641</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0956</v>
+        <v>-0.5506</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5523</v>
+        <v>0.3881</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7164</v>
+        <v>1.3582</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1324</v>
+        <v>-0.3213</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0022</v>
+        <v>-0.2114</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1346</v>
+        <v>-0.1099</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.894</v>
+        <v>0.3776</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.894</v>
+        <v>-0.8462</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. DE DOMINGO GARAY</t>
+          <t>G. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.419</v>
+        <v>-1.5018</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4115</v>
+        <v>-0.2783</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0075</v>
+        <v>-1.2235</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.324</v>
+        <v>-1.8696</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1467</v>
+        <v>-1.4286</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1773</v>
+        <v>-0.441</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1324</v>
+        <v>1.0418</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4943</v>
+        <v>0.3872</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6267</v>
+        <v>0.6546</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1916</v>
+        <v>-2.9114</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.641</v>
+        <v>-1.8158</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5506</v>
+        <v>-1.0956</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3881</v>
+        <v>1.5523</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3582</v>
+        <v>2.7164</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8607</v>
+        <v>-0.2905</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.1559</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3279</v>
+        <v>-0.1346</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3776</v>
+        <v>-0.894</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8462</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0572</v>
+        <v>-2.3994</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0959</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.153</v>
+        <v>-3.0168</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0473</v>
@@ -1312,13 +1312,13 @@
         <v>2.1344</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6965</v>
+        <v>-0.0387</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9567</v>
+        <v>-0.4352</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2602</v>
+        <v>0.3965</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4477</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9183</v>
+        <v>-5.3569</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.499</v>
+        <v>-4.556</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4193</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-6.0935</v>
@@ -1390,13 +1390,13 @@
         <v>2.1344</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2308</v>
+        <v>0.3306</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1508</v>
+        <v>-0.2078</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.5384</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5642</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.550699999999999</v>
+        <v>5.367900000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>1.681700000000001</v>
+        <v>3.4989</v>
       </c>
       <c r="F13" t="n">
-        <v>1.869199999999999</v>
+        <v>1.869</v>
       </c>
       <c r="G13" t="n">
         <v>-2.613700000000001</v>
@@ -1444,7 +1444,7 @@
         <v>11.1424</v>
       </c>
       <c r="K13" t="n">
-        <v>3.551</v>
+        <v>3.551000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>7.5913</v>
@@ -1468,10 +1468,10 @@
         <v>20.3735</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3909</v>
+        <v>0.4262000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.5933</v>
+        <v>-2.7761</v>
       </c>
       <c r="U13" t="n">
         <v>3.2023</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.1771</v>
+        <v>4.4746</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7615</v>
+        <v>2.0618</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4156</v>
+        <v>2.4128</v>
       </c>
       <c r="G14" t="n">
         <v>-1.5739</v>
@@ -1546,13 +1546,13 @@
         <v>2.3284</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0897</v>
+        <v>0.3872</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9444</v>
+        <v>-0.6441</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0341</v>
+        <v>1.0313</v>
       </c>
       <c r="V14" t="n">
         <v>5.2731</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1906</v>
+        <v>2.7785</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8712</v>
+        <v>2.5709</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3195</v>
+        <v>0.2076</v>
       </c>
       <c r="G15" t="n">
         <v>0.9581</v>
@@ -1624,13 +1624,13 @@
         <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0848</v>
+        <v>0.6727</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2165</v>
+        <v>-0.5168</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3013</v>
+        <v>1.1895</v>
       </c>
       <c r="V15" t="n">
         <v>2.1179</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9365</v>
+        <v>1.6429</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.339</v>
+        <v>-0.0387</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2755</v>
+        <v>1.6815</v>
       </c>
       <c r="G16" t="n">
         <v>0.7218</v>
@@ -1702,13 +1702,13 @@
         <v>1.1642</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6673</v>
+        <v>0.039</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.2325</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1346</v>
+        <v>0.2714</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2821</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.363</v>
+        <v>0.5994</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2741</v>
+        <v>1.3742</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9111</v>
+        <v>-0.7748</v>
       </c>
       <c r="G17" t="n">
         <v>0.8419</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4789</v>
+        <v>-0.2425</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2905</v>
+        <v>-0.1904</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1884</v>
+        <v>-0.0521</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1581</v>
+        <v>-0.925</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.2857</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0726</v>
+        <v>-0.6393</v>
       </c>
       <c r="G19" t="n">
         <v>1.7867</v>
@@ -1936,13 +1936,13 @@
         <v>1.7463</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.103</v>
+        <v>0.1301</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3859</v>
+        <v>-0.5861</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2829</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>-0.7075</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.437</v>
+        <v>-1.2278</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2598</v>
+        <v>0.3599</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6968</v>
+        <v>-1.5877</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7028</v>
@@ -2014,13 +2014,13 @@
         <v>1.1642</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1819</v>
+        <v>0.0272</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.5415</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4596</v>
+        <v>0.5687</v>
       </c>
       <c r="V20" t="n">
         <v>1.2239</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7503</v>
+        <v>-2.1779</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5031</v>
+        <v>-0.9035</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2471</v>
+        <v>-1.2744</v>
       </c>
       <c r="G21" t="n">
         <v>1.389</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6368</v>
+        <v>0.2092</v>
       </c>
       <c r="T21" t="n">
-        <v>0.498</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1389</v>
+        <v>0.1116</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8358</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9692</v>
+        <v>-3.5627</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9412</v>
+        <v>-3.6409</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.028</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>0.0533</v>
@@ -2170,13 +2170,13 @@
         <v>2.3284</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0536</v>
+        <v>0.4601</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8838</v>
+        <v>-0.5835</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9375</v>
+        <v>1.0437</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5537</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0977</v>
+        <v>-4.6795</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1669</v>
+        <v>-3.3671</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-1.3124</v>
       </c>
       <c r="G23" t="n">
         <v>0.0059</v>
@@ -2248,13 +2248,13 @@
         <v>0.9702</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8964</v>
+        <v>0.3146</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1951</v>
+        <v>-0.0051</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7012</v>
+        <v>0.3197</v>
       </c>
       <c r="V23" t="n">
         <v>-3.0597</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.551099999999998</v>
+        <v>-2.8835</v>
       </c>
       <c r="E24" t="n">
         <v>-1.8691</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6819</v>
+        <v>-1.0145</v>
       </c>
       <c r="G24" t="n">
         <v>2.6135</v>
@@ -2326,13 +2326,13 @@
         <v>11.642</v>
       </c>
       <c r="S24" t="n">
-        <v>1.3908</v>
+        <v>2.0582</v>
       </c>
       <c r="T24" t="n">
         <v>-3.2024</v>
       </c>
       <c r="U24" t="n">
-        <v>4.5931</v>
+        <v>5.2606</v>
       </c>
       <c r="V24" t="n">
         <v>1.1761</v>
